--- a/data/derived_data/2_RarefyData/mtd_samples_outAfterRare_ITS.xlsx
+++ b/data/derived_data/2_RarefyData/mtd_samples_outAfterRare_ITS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t xml:space="preserve">MS_163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_167</t>
   </si>
   <si>
     <t xml:space="preserve">MS_208</t>
@@ -3240,25 +3237,25 @@
         <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s">
         <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
         <v>52</v>
@@ -3279,24 +3276,24 @@
         <v>21</v>
       </c>
       <c r="P43" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="Q43" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="R43" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="S43" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
@@ -3305,13 +3302,13 @@
         <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G44" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H44" t="s">
         <v>43</v>
@@ -3329,10 +3326,10 @@
         <v>54</v>
       </c>
       <c r="M44" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N44" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O44" t="s">
         <v>21</v>
@@ -3341,30 +3338,30 @@
         <v>21</v>
       </c>
       <c r="Q44" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R44" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="S44" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -3385,13 +3382,13 @@
         <v>53</v>
       </c>
       <c r="L45" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="M45" t="s">
         <v>55</v>
       </c>
       <c r="N45" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="O45" t="s">
         <v>21</v>
@@ -3400,7 +3397,7 @@
         <v>21</v>
       </c>
       <c r="Q45" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R45" t="s">
         <v>97</v>
@@ -3411,31 +3408,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J46" t="s">
         <v>52</v>
@@ -3444,25 +3441,25 @@
         <v>53</v>
       </c>
       <c r="L46" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="M46" t="s">
         <v>55</v>
       </c>
       <c r="N46" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="O46" t="s">
         <v>21</v>
       </c>
       <c r="P46" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="Q46" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="R46" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="S46" t="s">
         <v>21</v>
@@ -3470,10 +3467,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
         <v>20</v>
@@ -3482,34 +3479,34 @@
         <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F47" t="s">
         <v>95</v>
       </c>
       <c r="G47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H47" t="s">
         <v>38</v>
       </c>
       <c r="I47" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J47" t="s">
         <v>52</v>
       </c>
       <c r="K47" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="L47" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="M47" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="N47" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="O47" t="s">
         <v>21</v>
@@ -3521,7 +3518,7 @@
         <v>45</v>
       </c>
       <c r="R47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S47" t="s">
         <v>21</v>
@@ -3529,10 +3526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
         <v>20</v>
@@ -3541,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="E48" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" t="s">
         <v>117</v>
-      </c>
-      <c r="F48" t="s">
-        <v>95</v>
-      </c>
-      <c r="G48" t="s">
-        <v>118</v>
       </c>
       <c r="H48" t="s">
         <v>38</v>
@@ -3559,16 +3556,16 @@
         <v>52</v>
       </c>
       <c r="K48" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N48" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O48" t="s">
         <v>21</v>
@@ -3580,7 +3577,7 @@
         <v>45</v>
       </c>
       <c r="R48" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S48" t="s">
         <v>21</v>
@@ -3588,72 +3585,72 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="F49" t="s">
         <v>41</v>
       </c>
       <c r="G49" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H49" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="I49" t="s">
         <v>44</v>
       </c>
       <c r="J49" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="L49" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="M49" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="O49" t="s">
         <v>21</v>
       </c>
       <c r="P49" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="Q49" t="s">
         <v>45</v>
       </c>
       <c r="R49" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="S49" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
@@ -3665,13 +3662,13 @@
         <v>41</v>
       </c>
       <c r="G50" t="s">
+        <v>127</v>
+      </c>
+      <c r="H50" t="s">
         <v>128</v>
       </c>
-      <c r="H50" t="s">
-        <v>129</v>
-      </c>
       <c r="I50" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J50" t="s">
         <v>21</v>
@@ -3701,18 +3698,18 @@
         <v>21</v>
       </c>
       <c r="S50" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
@@ -3724,10 +3721,10 @@
         <v>41</v>
       </c>
       <c r="G51" t="s">
+        <v>127</v>
+      </c>
+      <c r="H51" t="s">
         <v>128</v>
-      </c>
-      <c r="H51" t="s">
-        <v>129</v>
       </c>
       <c r="I51" t="s">
         <v>47</v>
@@ -3760,7 +3757,7 @@
         <v>21</v>
       </c>
       <c r="S51" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
@@ -3771,40 +3768,40 @@
         <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F52" t="s">
         <v>41</v>
       </c>
       <c r="G52" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="H52" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="I52" t="s">
         <v>47</v>
       </c>
       <c r="J52" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L52" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="M52" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="N52" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="O52" t="s">
         <v>21</v>
@@ -3816,10 +3813,10 @@
         <v>45</v>
       </c>
       <c r="R52" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="S52" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
@@ -3836,7 +3833,7 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F53" t="s">
         <v>41</v>
@@ -3851,19 +3848,19 @@
         <v>47</v>
       </c>
       <c r="J53" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="K53" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="L53" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M53" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="O53" t="s">
         <v>21</v>
@@ -3872,7 +3869,7 @@
         <v>21</v>
       </c>
       <c r="Q53" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="R53" t="s">
         <v>51</v>
@@ -3913,7 +3910,7 @@
         <v>67</v>
       </c>
       <c r="K54" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L54" t="s">
         <v>21</v>
@@ -3966,7 +3963,7 @@
         <v>43</v>
       </c>
       <c r="I55" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J55" t="s">
         <v>67</v>
@@ -4010,37 +4007,37 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F56" t="s">
         <v>41</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="H56" t="s">
         <v>43</v>
       </c>
       <c r="I56" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="K56" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L56" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="M56" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="N56" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="O56" t="s">
         <v>21</v>
@@ -4049,71 +4046,12 @@
         <v>21</v>
       </c>
       <c r="Q56" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="R56" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="S56" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>137</v>
-      </c>
-      <c r="B57" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57" t="s">
-        <v>110</v>
-      </c>
-      <c r="F57" t="s">
-        <v>41</v>
-      </c>
-      <c r="G57" t="s">
-        <v>96</v>
-      </c>
-      <c r="H57" t="s">
-        <v>43</v>
-      </c>
-      <c r="I57" t="s">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s">
-        <v>52</v>
-      </c>
-      <c r="K57" t="s">
-        <v>53</v>
-      </c>
-      <c r="L57" t="s">
-        <v>54</v>
-      </c>
-      <c r="M57" t="s">
-        <v>58</v>
-      </c>
-      <c r="N57" t="s">
-        <v>59</v>
-      </c>
-      <c r="O57" t="s">
-        <v>21</v>
-      </c>
-      <c r="P57" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>111</v>
-      </c>
-      <c r="R57" t="s">
-        <v>97</v>
-      </c>
-      <c r="S57" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data/derived_data/2_RarefyData/mtd_samples_outAfterRare_ITS.xlsx
+++ b/data/derived_data/2_RarefyData/mtd_samples_outAfterRare_ITS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">CT</t>
   </si>
   <si>
-    <t xml:space="preserve">na;No</t>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">CT_EXT_2</t>
@@ -128,9 +128,6 @@
     <t xml:space="preserve">CT_PCR_4</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_001</t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     <t xml:space="preserve">MS_098</t>
   </si>
   <si>
-    <t xml:space="preserve">Larva;na</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_106</t>
   </si>
   <si>
@@ -293,30 +287,27 @@
     <t xml:space="preserve">MS_116</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_121</t>
+    <t xml:space="preserve">MS_135</t>
   </si>
   <si>
     <t xml:space="preserve">G1_Pupae_Fruits</t>
   </si>
   <si>
+    <t xml:space="preserve">DaughterPupa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pupa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1_Adults_Fruits</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">DaughterPupa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pupa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G1_Adults_Fruits</t>
-  </si>
-  <si>
     <t xml:space="preserve">DaughterFly</t>
   </si>
   <si>
@@ -347,19 +338,7 @@
     <t xml:space="preserve">Pupae_Nat_Inf_Focal_Sites</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOM_CH_STA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pupae_Nat_Inf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_234</t>
+    <t xml:space="preserve">MS_246</t>
   </si>
   <si>
     <t xml:space="preserve">G1_PupalCase_Fruits</t>
@@ -368,9 +347,6 @@
     <t xml:space="preserve">PupalCase</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_246</t>
-  </si>
-  <si>
     <t xml:space="preserve">LOC</t>
   </si>
   <si>
@@ -402,9 +378,6 @@
   </si>
   <si>
     <t xml:space="preserve">MS_263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aunt;na</t>
   </si>
   <si>
     <t xml:space="preserve">MS_264</t>
@@ -951,7 +924,7 @@
         <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -1305,7 +1278,7 @@
         <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1541,7 +1514,7 @@
         <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
         <v>21</v>
@@ -1579,128 +1552,128 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>40</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>41</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>42</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>43</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
         <v>44</v>
       </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>45</v>
-      </c>
       <c r="R15" t="s">
         <v>21</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" t="s">
         <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>45</v>
-      </c>
-      <c r="R16" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
@@ -1709,19 +1682,19 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
         <v>40</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>41</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>42</v>
       </c>
-      <c r="H17" t="s">
-        <v>43</v>
-      </c>
       <c r="I17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J17" t="s">
         <v>21</v>
@@ -1745,58 +1718,58 @@
         <v>21</v>
       </c>
       <c r="Q17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R17" t="s">
         <v>21</v>
       </c>
       <c r="S17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>50</v>
-      </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" t="s">
         <v>51</v>
       </c>
-      <c r="H18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>52</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>53</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>54</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>55</v>
       </c>
-      <c r="N18" t="s">
-        <v>56</v>
-      </c>
       <c r="O18" t="s">
         <v>21</v>
       </c>
@@ -1804,21 +1777,21 @@
         <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
@@ -1827,35 +1800,35 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" t="s">
         <v>51</v>
       </c>
-      <c r="H19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" t="s">
-        <v>47</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>52</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>53</v>
       </c>
-      <c r="L19" t="s">
-        <v>54</v>
-      </c>
       <c r="M19" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" t="s">
         <v>58</v>
       </c>
-      <c r="N19" t="s">
-        <v>59</v>
-      </c>
       <c r="O19" t="s">
         <v>21</v>
       </c>
@@ -1863,80 +1836,80 @@
         <v>21</v>
       </c>
       <c r="Q19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" t="s">
         <v>60</v>
       </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="L20" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" t="s">
+        <v>63</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
         <v>44</v>
       </c>
-      <c r="J20" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" t="s">
-        <v>63</v>
-      </c>
-      <c r="N20" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>45</v>
-      </c>
       <c r="R20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
@@ -1945,57 +1918,57 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" t="s">
         <v>66</v>
       </c>
-      <c r="F21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>67</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
         <v>68</v>
       </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>69</v>
-      </c>
       <c r="R21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -2004,25 +1977,25 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" t="s">
         <v>66</v>
       </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" t="s">
-        <v>67</v>
-      </c>
       <c r="K22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
@@ -2040,21 +2013,21 @@
         <v>21</v>
       </c>
       <c r="Q22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -2063,25 +2036,25 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
         <v>66</v>
       </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" t="s">
-        <v>47</v>
-      </c>
-      <c r="J23" t="s">
-        <v>67</v>
-      </c>
       <c r="K23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
@@ -2099,21 +2072,21 @@
         <v>21</v>
       </c>
       <c r="Q23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -2122,25 +2095,25 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" t="s">
         <v>66</v>
       </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" t="s">
-        <v>67</v>
-      </c>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
@@ -2158,21 +2131,21 @@
         <v>21</v>
       </c>
       <c r="Q24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -2181,57 +2154,57 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" t="s">
         <v>66</v>
       </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>67</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
         <v>68</v>
       </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>69</v>
-      </c>
       <c r="R25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
@@ -2240,57 +2213,57 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" t="s">
         <v>66</v>
       </c>
-      <c r="F26" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>67</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
         <v>68</v>
       </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>69</v>
-      </c>
       <c r="R26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -2299,25 +2272,25 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" t="s">
         <v>66</v>
       </c>
-      <c r="F27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" t="s">
-        <v>51</v>
-      </c>
-      <c r="H27" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" t="s">
-        <v>67</v>
-      </c>
       <c r="K27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
@@ -2335,21 +2308,21 @@
         <v>21</v>
       </c>
       <c r="Q27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
@@ -2358,25 +2331,25 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" t="s">
         <v>66</v>
       </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>51</v>
-      </c>
-      <c r="H28" t="s">
-        <v>43</v>
-      </c>
-      <c r="I28" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" t="s">
-        <v>67</v>
-      </c>
       <c r="K28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
@@ -2394,48 +2367,48 @@
         <v>21</v>
       </c>
       <c r="Q28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
         <v>77</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" t="s">
-        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L29" t="s">
         <v>21</v>
@@ -2453,80 +2426,80 @@
         <v>21</v>
       </c>
       <c r="Q29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R29" t="s">
         <v>21</v>
       </c>
       <c r="S29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
         <v>80</v>
       </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" t="s">
         <v>81</v>
       </c>
-      <c r="F30" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" t="s">
+        <v>51</v>
+      </c>
+      <c r="K30" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>44</v>
+      </c>
+      <c r="R30" t="s">
         <v>82</v>
       </c>
-      <c r="H30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I30" t="s">
-        <v>47</v>
-      </c>
-      <c r="J30" t="s">
-        <v>52</v>
-      </c>
-      <c r="K30" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" t="s">
-        <v>54</v>
-      </c>
-      <c r="M30" t="s">
-        <v>55</v>
-      </c>
-      <c r="N30" t="s">
-        <v>56</v>
-      </c>
-      <c r="O30" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>45</v>
-      </c>
-      <c r="R30" t="s">
-        <v>83</v>
-      </c>
       <c r="S30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
@@ -2535,57 +2508,57 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" t="s">
         <v>81</v>
       </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" t="s">
+        <v>51</v>
+      </c>
+      <c r="K31" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>44</v>
+      </c>
+      <c r="R31" t="s">
         <v>82</v>
       </c>
-      <c r="H31" t="s">
-        <v>43</v>
-      </c>
-      <c r="I31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" t="s">
-        <v>52</v>
-      </c>
-      <c r="K31" t="s">
-        <v>53</v>
-      </c>
-      <c r="L31" t="s">
-        <v>54</v>
-      </c>
-      <c r="M31" t="s">
-        <v>55</v>
-      </c>
-      <c r="N31" t="s">
-        <v>56</v>
-      </c>
-      <c r="O31" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>45</v>
-      </c>
-      <c r="R31" t="s">
-        <v>83</v>
-      </c>
       <c r="S31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
         <v>25</v>
@@ -2594,57 +2567,57 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
       </c>
       <c r="G32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" t="s">
+        <v>67</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>68</v>
+      </c>
+      <c r="R32" t="s">
         <v>82</v>
       </c>
-      <c r="H32" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J32" t="s">
-        <v>67</v>
-      </c>
-      <c r="K32" t="s">
-        <v>68</v>
-      </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>69</v>
-      </c>
-      <c r="R32" t="s">
-        <v>83</v>
-      </c>
       <c r="S32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
@@ -2653,57 +2626,57 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
       </c>
       <c r="G33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>68</v>
+      </c>
+      <c r="R33" t="s">
         <v>82</v>
       </c>
-      <c r="H33" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" t="s">
-        <v>67</v>
-      </c>
-      <c r="K33" t="s">
-        <v>61</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>21</v>
-      </c>
-      <c r="P33" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>69</v>
-      </c>
-      <c r="R33" t="s">
-        <v>83</v>
-      </c>
       <c r="S33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
@@ -2712,57 +2685,57 @@
         <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
         <v>20</v>
       </c>
       <c r="G34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K34" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>68</v>
+      </c>
+      <c r="R34" t="s">
         <v>82</v>
       </c>
-      <c r="H34" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" t="s">
-        <v>47</v>
-      </c>
-      <c r="J34" t="s">
-        <v>67</v>
-      </c>
-      <c r="K34" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" t="s">
-        <v>21</v>
-      </c>
-      <c r="P34" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>69</v>
-      </c>
-      <c r="R34" t="s">
-        <v>83</v>
-      </c>
       <c r="S34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -2771,57 +2744,57 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
       </c>
       <c r="G35" t="s">
+        <v>81</v>
+      </c>
+      <c r="H35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" t="s">
+        <v>67</v>
+      </c>
+      <c r="L35" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>68</v>
+      </c>
+      <c r="R35" t="s">
         <v>82</v>
       </c>
-      <c r="H35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" t="s">
-        <v>67</v>
-      </c>
-      <c r="K35" t="s">
-        <v>68</v>
-      </c>
-      <c r="L35" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" t="s">
-        <v>21</v>
-      </c>
-      <c r="N35" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" t="s">
-        <v>21</v>
-      </c>
-      <c r="P35" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>69</v>
-      </c>
-      <c r="R35" t="s">
-        <v>83</v>
-      </c>
       <c r="S35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
@@ -2830,57 +2803,57 @@
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
       </c>
       <c r="G36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>68</v>
+      </c>
+      <c r="R36" t="s">
         <v>82</v>
       </c>
-      <c r="H36" t="s">
-        <v>43</v>
-      </c>
-      <c r="I36" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" t="s">
-        <v>61</v>
-      </c>
-      <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>69</v>
-      </c>
-      <c r="R36" t="s">
-        <v>83</v>
-      </c>
       <c r="S36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
         <v>25</v>
@@ -2889,57 +2862,57 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
       </c>
       <c r="G37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>68</v>
+      </c>
+      <c r="R37" t="s">
         <v>82</v>
       </c>
-      <c r="H37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" t="s">
-        <v>67</v>
-      </c>
-      <c r="K37" t="s">
-        <v>61</v>
-      </c>
-      <c r="L37" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" t="s">
-        <v>21</v>
-      </c>
-      <c r="P37" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>69</v>
-      </c>
-      <c r="R37" t="s">
-        <v>83</v>
-      </c>
       <c r="S37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
@@ -2948,46 +2921,46 @@
         <v>25</v>
       </c>
       <c r="E38" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L38" t="s">
+        <v>53</v>
+      </c>
+      <c r="M38" t="s">
+        <v>54</v>
+      </c>
+      <c r="N38" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>44</v>
+      </c>
+      <c r="R38" t="s">
         <v>94</v>
-      </c>
-      <c r="F38" t="s">
-        <v>95</v>
-      </c>
-      <c r="G38" t="s">
-        <v>96</v>
-      </c>
-      <c r="H38" t="s">
-        <v>43</v>
-      </c>
-      <c r="I38" t="s">
-        <v>47</v>
-      </c>
-      <c r="J38" t="s">
-        <v>52</v>
-      </c>
-      <c r="K38" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" t="s">
-        <v>54</v>
-      </c>
-      <c r="M38" t="s">
-        <v>55</v>
-      </c>
-      <c r="N38" t="s">
-        <v>56</v>
-      </c>
-      <c r="O38" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>45</v>
-      </c>
-      <c r="R38" t="s">
-        <v>97</v>
       </c>
       <c r="S38" t="s">
         <v>21</v>
@@ -2995,10 +2968,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
@@ -3007,46 +2980,46 @@
         <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
+        <v>46</v>
+      </c>
+      <c r="J39" t="s">
+        <v>51</v>
+      </c>
+      <c r="K39" t="s">
+        <v>52</v>
+      </c>
+      <c r="L39" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" t="s">
+        <v>54</v>
+      </c>
+      <c r="N39" t="s">
+        <v>55</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q39" t="s">
         <v>44</v>
       </c>
-      <c r="J39" t="s">
-        <v>52</v>
-      </c>
-      <c r="K39" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" t="s">
-        <v>54</v>
-      </c>
-      <c r="M39" t="s">
-        <v>55</v>
-      </c>
-      <c r="N39" t="s">
-        <v>56</v>
-      </c>
-      <c r="O39" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>45</v>
-      </c>
       <c r="R39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S39" t="s">
         <v>21</v>
@@ -3054,10 +3027,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
         <v>20</v>
@@ -3066,46 +3039,46 @@
         <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J40" t="s">
+        <v>51</v>
+      </c>
+      <c r="K40" t="s">
         <v>52</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>53</v>
       </c>
-      <c r="L40" t="s">
-        <v>54</v>
-      </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O40" t="s">
         <v>21</v>
       </c>
       <c r="P40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S40" t="s">
         <v>21</v>
@@ -3113,10 +3086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -3125,46 +3098,46 @@
         <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" t="s">
         <v>43</v>
       </c>
-      <c r="I41" t="s">
-        <v>47</v>
-      </c>
       <c r="J41" t="s">
+        <v>51</v>
+      </c>
+      <c r="K41" t="s">
         <v>52</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>53</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>54</v>
       </c>
-      <c r="M41" t="s">
-        <v>58</v>
-      </c>
       <c r="N41" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O41" t="s">
         <v>21</v>
       </c>
       <c r="P41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R41" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S41" t="s">
         <v>21</v>
@@ -3172,61 +3145,61 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>51</v>
+      </c>
+      <c r="K42" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" t="s">
+        <v>53</v>
+      </c>
+      <c r="M42" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" t="s">
+        <v>58</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
         <v>104</v>
       </c>
-      <c r="B42" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" t="s">
-        <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
-      </c>
-      <c r="H42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" t="s">
-        <v>44</v>
-      </c>
-      <c r="J42" t="s">
-        <v>52</v>
-      </c>
-      <c r="K42" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" t="s">
-        <v>54</v>
-      </c>
-      <c r="M42" t="s">
-        <v>55</v>
-      </c>
-      <c r="N42" t="s">
-        <v>56</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>45</v>
-      </c>
       <c r="R42" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
@@ -3246,31 +3219,31 @@
         <v>106</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G43" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
         <v>21</v>
       </c>
       <c r="J43" t="s">
+        <v>51</v>
+      </c>
+      <c r="K43" t="s">
         <v>52</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>53</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>54</v>
       </c>
-      <c r="M43" t="s">
-        <v>58</v>
-      </c>
       <c r="N43" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O43" t="s">
         <v>21</v>
@@ -3282,10 +3255,10 @@
         <v>107</v>
       </c>
       <c r="R43" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="S43" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -3296,52 +3269,52 @@
         <v>108</v>
       </c>
       <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
         <v>25</v>
-      </c>
-      <c r="D44" t="s">
-        <v>27</v>
       </c>
       <c r="E44" t="s">
         <v>109</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H44" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" t="s">
         <v>43</v>
       </c>
-      <c r="I44" t="s">
-        <v>21</v>
-      </c>
       <c r="J44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K44" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L44" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="N44" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="O44" t="s">
         <v>21</v>
       </c>
       <c r="P44" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="Q44" t="s">
+        <v>44</v>
+      </c>
+      <c r="R44" t="s">
         <v>110</v>
-      </c>
-      <c r="R44" t="s">
-        <v>97</v>
       </c>
       <c r="S44" t="s">
         <v>21</v>
@@ -3349,58 +3322,58 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
         <v>109</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G45" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H45" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" t="s">
         <v>43</v>
       </c>
-      <c r="I45" t="s">
-        <v>21</v>
-      </c>
       <c r="J45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K45" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L45" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O45" t="s">
         <v>21</v>
       </c>
       <c r="P45" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="Q45" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="R45" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="S45" t="s">
         <v>21</v>
@@ -3408,120 +3381,120 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="G46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H46" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="I46" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J46" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L46" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M46" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="O46" t="s">
         <v>21</v>
       </c>
       <c r="P46" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="Q46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R46" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="S46" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
         <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="G47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H47" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="I47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J47" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
         <v>44</v>
       </c>
-      <c r="J47" t="s">
-        <v>52</v>
-      </c>
-      <c r="K47" t="s">
-        <v>68</v>
-      </c>
-      <c r="L47" t="s">
-        <v>119</v>
-      </c>
-      <c r="M47" t="s">
-        <v>120</v>
-      </c>
-      <c r="N47" t="s">
-        <v>121</v>
-      </c>
-      <c r="O47" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>45</v>
-      </c>
       <c r="R47" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="S47" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
@@ -3532,122 +3505,122 @@
         <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" t="s">
+        <v>119</v>
+      </c>
+      <c r="H48" t="s">
+        <v>120</v>
+      </c>
+      <c r="I48" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>44</v>
+      </c>
+      <c r="R48" t="s">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s">
         <v>41</v>
-      </c>
-      <c r="G48" t="s">
-        <v>117</v>
-      </c>
-      <c r="H48" t="s">
-        <v>38</v>
-      </c>
-      <c r="I48" t="s">
-        <v>44</v>
-      </c>
-      <c r="J48" t="s">
-        <v>52</v>
-      </c>
-      <c r="K48" t="s">
-        <v>61</v>
-      </c>
-      <c r="L48" t="s">
-        <v>123</v>
-      </c>
-      <c r="M48" t="s">
-        <v>124</v>
-      </c>
-      <c r="N48" t="s">
-        <v>125</v>
-      </c>
-      <c r="O48" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>45</v>
-      </c>
-      <c r="R48" t="s">
-        <v>117</v>
-      </c>
-      <c r="S48" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
       </c>
       <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" t="s">
         <v>40</v>
       </c>
-      <c r="F49" t="s">
-        <v>41</v>
-      </c>
       <c r="G49" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" t="s">
+        <v>51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" t="s">
+        <v>53</v>
+      </c>
+      <c r="M49" t="s">
+        <v>57</v>
+      </c>
+      <c r="N49" t="s">
+        <v>58</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s">
         <v>44</v>
       </c>
-      <c r="J49" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>45</v>
-      </c>
       <c r="R49" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="S49" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C50" t="s">
         <v>20</v>
@@ -3656,25 +3629,25 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" t="s">
         <v>40</v>
       </c>
-      <c r="F50" t="s">
-        <v>41</v>
-      </c>
       <c r="G50" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="H50" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="K50" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="L50" t="s">
         <v>21</v>
@@ -3692,48 +3665,48 @@
         <v>21</v>
       </c>
       <c r="Q50" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="R50" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="S50" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
+        <v>65</v>
+      </c>
+      <c r="F51" t="s">
         <v>40</v>
       </c>
-      <c r="F51" t="s">
-        <v>41</v>
-      </c>
       <c r="G51" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J51" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="K51" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L51" t="s">
         <v>21</v>
@@ -3751,21 +3724,21 @@
         <v>21</v>
       </c>
       <c r="Q51" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="R51" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="S51" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
@@ -3774,34 +3747,34 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" t="s">
         <v>43</v>
       </c>
-      <c r="I52" t="s">
-        <v>47</v>
-      </c>
       <c r="J52" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K52" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L52" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M52" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="O52" t="s">
         <v>21</v>
@@ -3810,57 +3783,57 @@
         <v>21</v>
       </c>
       <c r="Q52" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="R52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G53" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
         <v>51</v>
       </c>
-      <c r="H53" t="s">
-        <v>43</v>
-      </c>
-      <c r="I53" t="s">
-        <v>47</v>
-      </c>
-      <c r="J53" t="s">
-        <v>67</v>
-      </c>
       <c r="K53" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M53" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="N53" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="O53" t="s">
         <v>21</v>
@@ -3869,189 +3842,12 @@
         <v>21</v>
       </c>
       <c r="Q53" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="R53" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="S53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" t="s">
-        <v>20</v>
-      </c>
-      <c r="D54" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F54" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" t="s">
-        <v>51</v>
-      </c>
-      <c r="H54" t="s">
-        <v>43</v>
-      </c>
-      <c r="I54" t="s">
-        <v>47</v>
-      </c>
-      <c r="J54" t="s">
-        <v>67</v>
-      </c>
-      <c r="K54" t="s">
-        <v>61</v>
-      </c>
-      <c r="L54" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" t="s">
-        <v>21</v>
-      </c>
-      <c r="N54" t="s">
-        <v>21</v>
-      </c>
-      <c r="O54" t="s">
-        <v>21</v>
-      </c>
-      <c r="P54" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>69</v>
-      </c>
-      <c r="R54" t="s">
-        <v>51</v>
-      </c>
-      <c r="S54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" t="s">
-        <v>66</v>
-      </c>
-      <c r="F55" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" t="s">
-        <v>51</v>
-      </c>
-      <c r="H55" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" t="s">
-        <v>44</v>
-      </c>
-      <c r="J55" t="s">
-        <v>67</v>
-      </c>
-      <c r="K55" t="s">
-        <v>61</v>
-      </c>
-      <c r="L55" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>69</v>
-      </c>
-      <c r="R55" t="s">
-        <v>51</v>
-      </c>
-      <c r="S55" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" t="s">
-        <v>109</v>
-      </c>
-      <c r="F56" t="s">
-        <v>41</v>
-      </c>
-      <c r="G56" t="s">
-        <v>96</v>
-      </c>
-      <c r="H56" t="s">
-        <v>43</v>
-      </c>
-      <c r="I56" t="s">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s">
-        <v>52</v>
-      </c>
-      <c r="K56" t="s">
-        <v>53</v>
-      </c>
-      <c r="L56" t="s">
-        <v>54</v>
-      </c>
-      <c r="M56" t="s">
-        <v>58</v>
-      </c>
-      <c r="N56" t="s">
-        <v>59</v>
-      </c>
-      <c r="O56" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>110</v>
-      </c>
-      <c r="R56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S56" t="s">
         <v>21</v>
       </c>
     </row>
